--- a/consent_forms/039_treasury_budget_disclosure_consent_form--consent_forms.xlsx
+++ b/consent_forms/039_treasury_budget_disclosure_consent_form--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -784,8 +784,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -813,12 +813,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -830,12 +830,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -847,12 +847,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'bank',_'label':_'bank'}</t>
+          <t>bank</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'bank', 'label': 'Bank'}</t>
+          <t>Bank</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'credit_union',_'label':_'credit_union'}</t>
+          <t>credit_union</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'credit_union', 'label': 'Credit Union'}</t>
+          <t>Credit Union</t>
         </is>
       </c>
     </row>
@@ -881,12 +881,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'investment_institution',_'label':_'investment_institution'}</t>
+          <t>investment_institution</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'investment_institution', 'label': 'Investment Institution'}</t>
+          <t>Investment Institution</t>
         </is>
       </c>
     </row>
@@ -898,12 +898,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'government_agency',_'label':_'government_agency'}</t>
+          <t>government_agency</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'government_agency', 'label': 'Government Agency'}</t>
+          <t>Government Agency</t>
         </is>
       </c>
     </row>
@@ -915,12 +915,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'commercial',_'label':_'commercial'}</t>
+          <t>commercial</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'commercial', 'label': 'Commercial'}</t>
+          <t>Commercial</t>
         </is>
       </c>
     </row>
@@ -932,12 +932,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'consumer',_'label':_'consumer'}</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'consumer', 'label': 'Consumer'}</t>
+          <t>Consumer</t>
         </is>
       </c>
     </row>
@@ -949,12 +949,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'industrial',_'label':_'industrial'}</t>
+          <t>industrial</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'industrial', 'label': 'Industrial'}</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -966,12 +966,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'investment',_'label':_'investment'}</t>
+          <t>investment</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'investment', 'label': 'Investment'}</t>
+          <t>Investment</t>
         </is>
       </c>
     </row>
@@ -983,12 +983,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'non_commercial',_'label':_'non-commercial'}</t>
+          <t>non-commercial</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'non_commercial', 'label': 'Non-Commercial'}</t>
+          <t>Non-Commercial</t>
         </is>
       </c>
     </row>
@@ -1000,12 +1000,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'public',_'label':_'public'}</t>
+          <t>public</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'public', 'label': 'Public'}</t>
+          <t>Public</t>
         </is>
       </c>
     </row>
@@ -1017,12 +1017,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1034,12 +1034,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'bank',_'label':_'bank'}</t>
+          <t>bank</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'bank', 'label': 'Bank'}</t>
+          <t>Bank</t>
         </is>
       </c>
     </row>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'credit_union',_'label':_'credit_union'}</t>
+          <t>credit_union</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'credit_union', 'label': 'Credit Union'}</t>
+          <t>Credit Union</t>
         </is>
       </c>
     </row>
@@ -1068,12 +1068,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'government_agency',_'label':_'government_agency'}</t>
+          <t>government_agency</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'government_agency', 'label': 'Government Agency'}</t>
+          <t>Government Agency</t>
         </is>
       </c>
     </row>
@@ -1085,12 +1085,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'institution',_'label':_'institution'}</t>
+          <t>institution</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'institution', 'label': 'Institution'}</t>
+          <t>Institution</t>
         </is>
       </c>
     </row>
@@ -1119,12 +1119,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'subsidiary',_'label':_'subsidiary'}</t>
+          <t>subsidiary</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'subsidiary', 'label': 'Subsidiary'}</t>
+          <t>Subsidiary</t>
         </is>
       </c>
     </row>
@@ -1136,12 +1136,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'branch',_'label':_'branch'}</t>
+          <t>branch</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'branch', 'label': 'Branch'}</t>
+          <t>Branch</t>
         </is>
       </c>
     </row>
